--- a/Project Outputs for BYS_hyperloop/BYS_hyperloop_BOM.xlsx
+++ b/Project Outputs for BYS_hyperloop/BYS_hyperloop_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samet AKIN\Desktop\samet\altium_project\BYS_hyperloop\Project Outputs for BYS_hyperloop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBAC8E03-EFB7-450F-AA51-DEE4B067A1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31A29C38-600F-490B-BFDC-0564C15300CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3348" yWindow="804" windowWidth="17280" windowHeight="8964" xr2:uid="{A4FEC59F-329D-46DE-B7F3-22B9BC0100BA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7045F3FE-3CDA-4DCA-98B9-6BB2B3FD5690}"/>
   </bookViews>
   <sheets>
     <sheet name="BYS_hyperloop_BOM" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="121">
   <si>
     <t>Comment</t>
   </si>
@@ -110,7 +110,7 @@
     <t>0603YD225KAT4A</t>
   </si>
   <si>
-    <t>C1607</t>
+    <t>C23630</t>
   </si>
   <si>
     <t>0.1µF</t>
@@ -125,7 +125,7 @@
     <t>06035G104ZAT2A</t>
   </si>
   <si>
-    <t>C1590</t>
+    <t>C14663</t>
   </si>
   <si>
     <t>BAS20W-7-F</t>
@@ -209,6 +209,9 @@
     <t>JST XH B2B-XH-A</t>
   </si>
   <si>
+    <t>C2908600</t>
+  </si>
+  <si>
     <t>B5B-XH-A(LF)(SN)</t>
   </si>
   <si>
@@ -221,6 +224,9 @@
     <t>JST XH B5B-XH-A</t>
   </si>
   <si>
+    <t>C157991</t>
+  </si>
+  <si>
     <t>SMT XT90 CONNECTOR</t>
   </si>
   <si>
@@ -254,6 +260,9 @@
     <t>TO-263-3-2</t>
   </si>
   <si>
+    <t>C2909634</t>
+  </si>
+  <si>
     <t>ZXTN25060BFHTA</t>
   </si>
   <si>
@@ -266,6 +275,9 @@
     <t>DIODES SOT-23-3</t>
   </si>
   <si>
+    <t>C2145</t>
+  </si>
+  <si>
     <t>100 kOhms</t>
   </si>
   <si>
@@ -281,7 +293,7 @@
     <t>TNPW0805100KFEEA</t>
   </si>
   <si>
-    <t>C25611</t>
+    <t>C149504</t>
   </si>
   <si>
     <t>0 Ohms</t>
@@ -347,7 +359,7 @@
     <t>CPF0603B10KE</t>
   </si>
   <si>
-    <t>C15401</t>
+    <t>C25804</t>
   </si>
   <si>
     <t>22 kOhms</t>
@@ -786,7 +798,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83CB3261-A55B-4207-B8E9-917603383929}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC5C0A15-0647-42EA-9B98-0099017EF8A2}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1041,67 +1053,71 @@
       <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="F12" s="1">
         <v>3</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="G12" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F13" s="1">
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1110,84 +1126,88 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="F15" s="1">
         <v>2</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="F16" s="1">
         <v>1</v>
       </c>
-      <c r="G16" s="1"/>
+      <c r="G16" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F18" s="1">
         <v>2</v>
@@ -1196,19 +1216,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F19" s="1">
         <v>2</v>
@@ -1217,42 +1237,42 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F20" s="1">
         <v>3</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F21" s="1">
         <v>3</v>
@@ -1261,88 +1281,88 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F22" s="1">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F23" s="1">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F25" s="1">
         <v>1</v>
